--- a/research/traditional_assets/database/data/belgium/belgium_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_software_system_application.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>0.003631082062454612</v>
+        <v>-0.0321390937829294</v>
       </c>
       <c r="H2">
-        <v>-0.09368191721132899</v>
+        <v>-0.1159114857744995</v>
       </c>
       <c r="I2">
-        <v>-0.1517792302106028</v>
+        <v>-0.1780821917808219</v>
       </c>
       <c r="J2">
-        <v>-0.1517792302106028</v>
+        <v>-0.1780821917808219</v>
       </c>
       <c r="K2">
-        <v>-33.6</v>
+        <v>-37.4</v>
       </c>
       <c r="L2">
-        <v>-0.2440087145969499</v>
+        <v>-0.1970495258166491</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>29.8</v>
+        <v>44.6</v>
       </c>
       <c r="V2">
-        <v>0.05234498506938346</v>
+        <v>0.3360964581763377</v>
       </c>
       <c r="W2">
-        <v>3.733333333333333</v>
+        <v>-0.1491228070175439</v>
       </c>
       <c r="X2">
-        <v>0.07367603764172646</v>
+        <v>0.1816285591016718</v>
       </c>
       <c r="Y2">
-        <v>3.659657295691607</v>
+        <v>-0.3307513661192156</v>
       </c>
       <c r="Z2">
-        <v>3.394970414201183</v>
+        <v>2.40253164556962</v>
       </c>
       <c r="AA2">
-        <v>-0.5152859960552267</v>
+        <v>-0.4278481012658227</v>
       </c>
       <c r="AB2">
-        <v>0.07000962459515869</v>
+        <v>0.1253141402170796</v>
       </c>
       <c r="AC2">
-        <v>-0.5852956206503854</v>
+        <v>-0.5531622414829023</v>
       </c>
       <c r="AD2">
-        <v>46.2</v>
+        <v>98.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>46.2</v>
+        <v>98.7</v>
       </c>
       <c r="AG2">
-        <v>16.4</v>
+        <v>54.1</v>
       </c>
       <c r="AH2">
-        <v>0.07506092607636068</v>
+        <v>0.4265341400172861</v>
       </c>
       <c r="AI2">
-        <v>0.1553463349024883</v>
+        <v>0.3453463960811756</v>
       </c>
       <c r="AJ2">
-        <v>0.02800068294348643</v>
+        <v>0.2896145610278373</v>
       </c>
       <c r="AK2">
-        <v>0.06128550074738417</v>
+        <v>0.2242951907131012</v>
       </c>
       <c r="AL2">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="AM2">
-        <v>2.241</v>
+        <v>3.587</v>
       </c>
       <c r="AN2">
-        <v>-3.186206896551724</v>
+        <v>-3.682835820895523</v>
       </c>
       <c r="AO2">
-        <v>-9.047619047619047</v>
+        <v>-8.779220779220779</v>
       </c>
       <c r="AP2">
-        <v>-1.131034482758621</v>
+        <v>-2.01865671641791</v>
       </c>
       <c r="AQ2">
-        <v>-9.32619366354306</v>
+        <v>-9.422916085865625</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.003631082062454612</v>
+        <v>-0.0321390937829294</v>
       </c>
       <c r="H3">
-        <v>-0.09368191721132899</v>
+        <v>-0.1159114857744995</v>
       </c>
       <c r="I3">
-        <v>-0.1517792302106028</v>
+        <v>-0.1780821917808219</v>
       </c>
       <c r="J3">
-        <v>-0.1517792302106028</v>
+        <v>-0.1780821917808219</v>
       </c>
       <c r="K3">
-        <v>-33.6</v>
+        <v>-37.4</v>
       </c>
       <c r="L3">
-        <v>-0.2440087145969499</v>
+        <v>-0.1970495258166491</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>29.8</v>
+        <v>44.6</v>
       </c>
       <c r="V3">
-        <v>0.05234498506938346</v>
+        <v>0.3360964581763377</v>
       </c>
       <c r="W3">
-        <v>3.733333333333333</v>
+        <v>-0.1491228070175439</v>
       </c>
       <c r="X3">
-        <v>0.07367603764172646</v>
+        <v>0.1816285591016718</v>
       </c>
       <c r="Y3">
-        <v>3.659657295691607</v>
+        <v>-0.3307513661192156</v>
       </c>
       <c r="Z3">
-        <v>3.394970414201183</v>
+        <v>2.40253164556962</v>
       </c>
       <c r="AA3">
-        <v>-0.5152859960552267</v>
+        <v>-0.4278481012658227</v>
       </c>
       <c r="AB3">
-        <v>0.07000962459515869</v>
+        <v>0.1253141402170796</v>
       </c>
       <c r="AC3">
-        <v>-0.5852956206503854</v>
+        <v>-0.5531622414829023</v>
       </c>
       <c r="AD3">
-        <v>46.2</v>
+        <v>98.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>46.2</v>
+        <v>98.7</v>
       </c>
       <c r="AG3">
-        <v>16.4</v>
+        <v>54.1</v>
       </c>
       <c r="AH3">
-        <v>0.07506092607636068</v>
+        <v>0.4265341400172861</v>
       </c>
       <c r="AI3">
-        <v>0.1553463349024883</v>
+        <v>0.3453463960811756</v>
       </c>
       <c r="AJ3">
-        <v>0.02800068294348643</v>
+        <v>0.2896145610278373</v>
       </c>
       <c r="AK3">
-        <v>0.06128550074738417</v>
+        <v>0.2242951907131012</v>
       </c>
       <c r="AL3">
-        <v>2.31</v>
+        <v>3.85</v>
       </c>
       <c r="AM3">
-        <v>2.241</v>
+        <v>3.587</v>
       </c>
       <c r="AN3">
-        <v>-3.186206896551724</v>
+        <v>-3.682835820895523</v>
       </c>
       <c r="AO3">
-        <v>-9.047619047619047</v>
+        <v>-8.779220779220779</v>
       </c>
       <c r="AP3">
-        <v>-1.131034482758621</v>
+        <v>-2.01865671641791</v>
       </c>
       <c r="AQ3">
-        <v>-9.32619366354306</v>
+        <v>-9.422916085865625</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/belgium/belgium_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_software_system_application.xlsx
@@ -588,22 +588,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.0321390937829294</v>
+        <v>-0.02379819133745835</v>
       </c>
       <c r="H2">
-        <v>-0.1159114857744995</v>
+        <v>-0.1166111375535459</v>
       </c>
       <c r="I2">
-        <v>-0.1780821917808219</v>
+        <v>-0.1404093288910043</v>
       </c>
       <c r="J2">
-        <v>-0.1780821917808219</v>
+        <v>-0.1404093288910043</v>
       </c>
       <c r="K2">
-        <v>-37.4</v>
+        <v>-51.1</v>
       </c>
       <c r="L2">
-        <v>-0.1970495258166491</v>
+        <v>-0.2432175154688244</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +627,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>44.6</v>
+        <v>27</v>
       </c>
       <c r="V2">
-        <v>0.3360964581763377</v>
+        <v>0.2641878669275929</v>
       </c>
       <c r="W2">
-        <v>-0.1491228070175439</v>
+        <v>-0.2734082397003745</v>
       </c>
       <c r="X2">
-        <v>0.1816285591016718</v>
+        <v>0.179445198373796</v>
       </c>
       <c r="Y2">
-        <v>-0.3307513661192156</v>
+        <v>-0.4528534380741706</v>
       </c>
       <c r="Z2">
-        <v>2.40253164556962</v>
+        <v>2.629536921151438</v>
       </c>
       <c r="AA2">
-        <v>-0.4278481012658227</v>
+        <v>-0.3692115143929911</v>
       </c>
       <c r="AB2">
-        <v>0.1253141402170796</v>
+        <v>0.1011979812326164</v>
       </c>
       <c r="AC2">
-        <v>-0.5531622414829023</v>
+        <v>-0.4704094956256075</v>
       </c>
       <c r="AD2">
-        <v>98.7</v>
+        <v>137.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>98.7</v>
+        <v>137.5</v>
       </c>
       <c r="AG2">
-        <v>54.1</v>
+        <v>110.5</v>
       </c>
       <c r="AH2">
-        <v>0.4265341400172861</v>
+        <v>0.5736337088026701</v>
       </c>
       <c r="AI2">
-        <v>0.3453463960811756</v>
+        <v>0.486553432413305</v>
       </c>
       <c r="AJ2">
-        <v>0.2896145610278373</v>
+        <v>0.5195110484250118</v>
       </c>
       <c r="AK2">
-        <v>0.2242951907131012</v>
+        <v>0.4323161189358373</v>
       </c>
       <c r="AL2">
-        <v>3.85</v>
+        <v>14.1</v>
       </c>
       <c r="AM2">
-        <v>3.587</v>
+        <v>13.935</v>
       </c>
       <c r="AN2">
-        <v>-3.682835820895523</v>
+        <v>-6.455399061032864</v>
       </c>
       <c r="AO2">
-        <v>-8.779220779220779</v>
+        <v>-2.092198581560284</v>
       </c>
       <c r="AP2">
-        <v>-2.01865671641791</v>
+        <v>-5.187793427230047</v>
       </c>
       <c r="AQ2">
-        <v>-9.422916085865625</v>
+        <v>-2.11697165410836</v>
       </c>
     </row>
     <row r="3">
@@ -713,22 +713,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.0321390937829294</v>
+        <v>-0.02379819133745835</v>
       </c>
       <c r="H3">
-        <v>-0.1159114857744995</v>
+        <v>-0.1166111375535459</v>
       </c>
       <c r="I3">
-        <v>-0.1780821917808219</v>
+        <v>-0.1404093288910043</v>
       </c>
       <c r="J3">
-        <v>-0.1780821917808219</v>
+        <v>-0.1404093288910043</v>
       </c>
       <c r="K3">
-        <v>-37.4</v>
+        <v>-51.1</v>
       </c>
       <c r="L3">
-        <v>-0.1970495258166491</v>
+        <v>-0.2432175154688244</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>44.6</v>
+        <v>27</v>
       </c>
       <c r="V3">
-        <v>0.3360964581763377</v>
+        <v>0.2641878669275929</v>
       </c>
       <c r="W3">
-        <v>-0.1491228070175439</v>
+        <v>-0.2734082397003745</v>
       </c>
       <c r="X3">
-        <v>0.1816285591016718</v>
+        <v>0.179445198373796</v>
       </c>
       <c r="Y3">
-        <v>-0.3307513661192156</v>
+        <v>-0.4528534380741706</v>
       </c>
       <c r="Z3">
-        <v>2.40253164556962</v>
+        <v>2.629536921151438</v>
       </c>
       <c r="AA3">
-        <v>-0.4278481012658227</v>
+        <v>-0.3692115143929911</v>
       </c>
       <c r="AB3">
-        <v>0.1253141402170796</v>
+        <v>0.1011979812326164</v>
       </c>
       <c r="AC3">
-        <v>-0.5531622414829023</v>
+        <v>-0.4704094956256075</v>
       </c>
       <c r="AD3">
-        <v>98.7</v>
+        <v>137.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>98.7</v>
+        <v>137.5</v>
       </c>
       <c r="AG3">
-        <v>54.1</v>
+        <v>110.5</v>
       </c>
       <c r="AH3">
-        <v>0.4265341400172861</v>
+        <v>0.5736337088026701</v>
       </c>
       <c r="AI3">
-        <v>0.3453463960811756</v>
+        <v>0.486553432413305</v>
       </c>
       <c r="AJ3">
-        <v>0.2896145610278373</v>
+        <v>0.5195110484250118</v>
       </c>
       <c r="AK3">
-        <v>0.2242951907131012</v>
+        <v>0.4323161189358373</v>
       </c>
       <c r="AL3">
-        <v>3.85</v>
+        <v>14.1</v>
       </c>
       <c r="AM3">
-        <v>3.587</v>
+        <v>13.935</v>
       </c>
       <c r="AN3">
-        <v>-3.682835820895523</v>
+        <v>-6.455399061032864</v>
       </c>
       <c r="AO3">
-        <v>-8.779220779220779</v>
+        <v>-2.092198581560284</v>
       </c>
       <c r="AP3">
-        <v>-2.01865671641791</v>
+        <v>-5.187793427230047</v>
       </c>
       <c r="AQ3">
-        <v>-9.422916085865625</v>
+        <v>-2.11697165410836</v>
       </c>
     </row>
   </sheetData>
